--- a/data/trans_orig/P0802-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P0802-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a subir varios pisos en 2007</t>
+          <t>Población según limitación a subir varios pisos en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>695511</t>
+          <t>693063</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>751001</t>
+          <t>753188</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>678978</t>
+          <t>680561</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>751194</t>
+          <t>755191</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1391458</t>
+          <t>1394318</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1486420</t>
+          <t>1489494</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,47%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>195286</t>
+          <t>196135</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>245820</t>
+          <t>246328</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>400457</t>
+          <t>400256</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>466318</t>
+          <t>467942</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>615440</t>
+          <t>608060</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>698975</t>
+          <t>694805</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69832</t>
+          <t>70629</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>106853</t>
+          <t>105507</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>142380</t>
+          <t>141665</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>190423</t>
+          <t>190105</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>224168</t>
+          <t>224528</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>283694</t>
+          <t>282932</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1557777</t>
+          <t>1559416</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1597530</t>
+          <t>1599721</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1425365</t>
+          <t>1427202</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1470029</t>
+          <t>1472327</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2998035</t>
+          <t>3000792</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3058255</t>
+          <t>3059082</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75492</t>
+          <t>72392</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>111074</t>
+          <t>110250</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>84064</t>
+          <t>80704</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>122369</t>
+          <t>119693</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>164604</t>
+          <t>163859</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>218250</t>
+          <t>217251</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14778</t>
+          <t>15215</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34028</t>
+          <t>33411</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26597</t>
+          <t>27042</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50668</t>
+          <t>50686</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45339</t>
+          <t>46454</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76250</t>
+          <t>77159</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>501888</t>
+          <t>503162</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>526554</t>
+          <t>528323</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>412929</t>
+          <t>410798</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>440402</t>
+          <t>439716</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>924855</t>
+          <t>923111</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>961248</t>
+          <t>961000</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,5%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15124</t>
+          <t>14494</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35871</t>
+          <t>35998</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27463</t>
+          <t>27766</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52332</t>
+          <t>53715</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49110</t>
+          <t>48520</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79638</t>
+          <t>80905</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5667</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20671</t>
+          <t>21345</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>5597</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17764</t>
+          <t>18747</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13909</t>
+          <t>12925</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34577</t>
+          <t>32940</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2781204</t>
+          <t>2780770</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2855843</t>
+          <t>2860304</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2540493</t>
+          <t>2542685</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2643450</t>
+          <t>2641918</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5345698</t>
+          <t>5353005</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5477417</t>
+          <t>5475675</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,27%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>303585</t>
+          <t>301996</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>372599</t>
+          <t>371394</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>528502</t>
+          <t>532418</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>619138</t>
+          <t>623494</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>851342</t>
+          <t>852849</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>963313</t>
+          <t>960674</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>102165</t>
+          <t>101039</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>144279</t>
+          <t>143626</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>186830</t>
+          <t>184782</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>243588</t>
+          <t>243533</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>298915</t>
+          <t>301104</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>372125</t>
+          <t>371522</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a subir varios pisos en 2012</t>
+          <t>Población según limitación a subir varios pisos en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>621060</t>
+          <t>618146</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>683828</t>
+          <t>680832</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>645818</t>
+          <t>643770</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>719466</t>
+          <t>721779</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1287681</t>
+          <t>1282634</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1381958</t>
+          <t>1379705</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>59,69%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>173287</t>
+          <t>174298</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>224816</t>
+          <t>228237</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>349431</t>
+          <t>347008</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>417845</t>
+          <t>414576</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>537975</t>
+          <t>541639</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>622011</t>
+          <t>628770</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>101456</t>
+          <t>105011</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>147984</t>
+          <t>150185</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>242784</t>
+          <t>242411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>304159</t>
+          <t>305417</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>360579</t>
+          <t>360253</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>435372</t>
+          <t>438533</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1757387</t>
+          <t>1758164</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1810686</t>
+          <t>1811499</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1504448</t>
+          <t>1505376</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1565714</t>
+          <t>1568898</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3279385</t>
+          <t>3282329</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3361586</t>
+          <t>3362606</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,45%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>113525</t>
+          <t>115008</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>162458</t>
+          <t>159754</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>132267</t>
+          <t>133698</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>185832</t>
+          <t>184169</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>258441</t>
+          <t>261240</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>330594</t>
+          <t>329122</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27190</t>
+          <t>25590</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53946</t>
+          <t>53439</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48746</t>
+          <t>46719</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83484</t>
+          <t>82836</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81011</t>
+          <t>82026</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>122903</t>
+          <t>124520</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>431601</t>
+          <t>431005</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>456796</t>
+          <t>456401</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>406022</t>
+          <t>406728</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>431139</t>
+          <t>430954</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>845778</t>
+          <t>847270</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>882178</t>
+          <t>881082</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16305</t>
+          <t>16213</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37999</t>
+          <t>38190</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19429</t>
+          <t>19707</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42131</t>
+          <t>42254</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40049</t>
+          <t>40860</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70478</t>
+          <t>70955</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21647</t>
+          <t>21871</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4189</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16246</t>
+          <t>18408</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12870</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32402</t>
+          <t>32269</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2834463</t>
+          <t>2841998</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2925930</t>
+          <t>2928321</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2584804</t>
+          <t>2590538</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2696765</t>
+          <t>2694212</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5459158</t>
+          <t>5455302</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5592624</t>
+          <t>5592041</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,24%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>323314</t>
+          <t>325218</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>399835</t>
+          <t>396518</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>521725</t>
+          <t>527652</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>614063</t>
+          <t>613975</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>869485</t>
+          <t>866673</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>985382</t>
+          <t>992009</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>147421</t>
+          <t>146872</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>204027</t>
+          <t>202200</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>310696</t>
+          <t>308368</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>382599</t>
+          <t>383106</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>472792</t>
+          <t>473482</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>565009</t>
+          <t>565816</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a subir varios pisos en 2016</t>
+          <t>Población según limitación a subir varios pisos en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>478629</t>
+          <t>470715</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>527392</t>
+          <t>523161</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>478920</t>
+          <t>473128</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>541603</t>
+          <t>541951</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>966126</t>
+          <t>966462</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1051167</t>
+          <t>1053098</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,21%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>137918</t>
+          <t>138579</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>179832</t>
+          <t>181512</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>251429</t>
+          <t>249149</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>307632</t>
+          <t>309276</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>399536</t>
+          <t>396113</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>474752</t>
+          <t>473672</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,08%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>78555</t>
+          <t>76992</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>112441</t>
+          <t>112518</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>183870</t>
+          <t>181177</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>239575</t>
+          <t>238740</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>272438</t>
+          <t>275081</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>340510</t>
+          <t>341794</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1854474</t>
+          <t>1852212</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1905559</t>
+          <t>1908508</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1679338</t>
+          <t>1681880</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1747615</t>
+          <t>1746242</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3551739</t>
+          <t>3551320</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3634150</t>
+          <t>3633735</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,4%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>127638</t>
+          <t>124134</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>173166</t>
+          <t>175199</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>158909</t>
+          <t>159853</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>214542</t>
+          <t>210982</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>297324</t>
+          <t>300240</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>369089</t>
+          <t>371765</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36263</t>
+          <t>35164</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65008</t>
+          <t>63786</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72795</t>
+          <t>70825</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>111927</t>
+          <t>110542</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>115062</t>
+          <t>115065</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>162284</t>
+          <t>162779</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>489018</t>
+          <t>487943</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>516115</t>
+          <t>514832</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>486618</t>
+          <t>487617</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>514715</t>
+          <t>516084</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>984299</t>
+          <t>986828</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1024517</t>
+          <t>1026049</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,62%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21031</t>
+          <t>21722</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46147</t>
+          <t>46609</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20124</t>
+          <t>19003</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41703</t>
+          <t>42284</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47015</t>
+          <t>45566</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79360</t>
+          <t>80234</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18697</t>
+          <t>19730</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8471</t>
+          <t>9267</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26954</t>
+          <t>27425</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17030</t>
+          <t>17929</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40066</t>
+          <t>41396</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2841961</t>
+          <t>2844492</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2929907</t>
+          <t>2925802</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2674036</t>
+          <t>2669453</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2778852</t>
+          <t>2778810</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5541841</t>
+          <t>5547860</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5676301</t>
+          <t>5674869</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,13%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>301147</t>
+          <t>306258</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>375566</t>
+          <t>374425</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>450832</t>
+          <t>449960</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>537843</t>
+          <t>534134</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>776808</t>
+          <t>775378</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>886108</t>
+          <t>884801</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>130299</t>
+          <t>130412</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178140</t>
+          <t>179651</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>280371</t>
+          <t>281476</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>350895</t>
+          <t>358064</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>426895</t>
+          <t>429121</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>515848</t>
+          <t>517255</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a subir varios pisos en 2023</t>
+          <t>Población según limitación a subir varios pisos en 2023 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>311288</t>
+          <t>310477</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>351348</t>
+          <t>350432</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>319902</t>
+          <t>321408</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>364340</t>
+          <t>364117</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>644908</t>
+          <t>645530</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>704433</t>
+          <t>703215</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,38%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88274</t>
+          <t>91365</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>122469</t>
+          <t>122896</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>206655</t>
+          <t>207304</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>247588</t>
+          <t>245748</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>305949</t>
+          <t>305821</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>359263</t>
+          <t>358435</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,23%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65707</t>
+          <t>65353</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>93600</t>
+          <t>93841</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>167327</t>
+          <t>167629</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>203146</t>
+          <t>202408</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>244504</t>
+          <t>241712</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>290390</t>
+          <t>287748</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1230610</t>
+          <t>1203371</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2006011</t>
+          <t>2007315</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1893793</t>
+          <t>1894977</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2018316</t>
+          <t>2019373</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3117838</t>
+          <t>3007035</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3954962</t>
+          <t>3952632</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,29%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>219933</t>
+          <t>217030</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1019589</t>
+          <t>1056913</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>165591</t>
+          <t>164655</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>259341</t>
+          <t>262315</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>433654</t>
+          <t>437735</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1292410</t>
+          <t>1407661</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41121</t>
+          <t>41169</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77146</t>
+          <t>79803</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55241</t>
+          <t>54139</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91686</t>
+          <t>90330</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>107558</t>
+          <t>106419</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159013</t>
+          <t>159869</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>588849</t>
+          <t>589637</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>612307</t>
+          <t>611658</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>587667</t>
+          <t>587951</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>610837</t>
+          <t>611023</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1185415</t>
+          <t>1186618</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1218631</t>
+          <t>1218713</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23414</t>
+          <t>23133</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44277</t>
+          <t>43480</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35660</t>
+          <t>35200</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55836</t>
+          <t>54298</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63128</t>
+          <t>62272</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91191</t>
+          <t>90429</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6993</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18379</t>
+          <t>19437</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10281</t>
+          <t>10471</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23609</t>
+          <t>22399</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19978</t>
+          <t>19913</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39112</t>
+          <t>37929</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2118206</t>
+          <t>2144647</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2937105</t>
+          <t>2937065</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2810091</t>
+          <t>2813893</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3029657</t>
+          <t>3019975</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,17 +8331,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5597865</t>
+          <t>5597866</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4845170</t>
+          <t>4889661</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5837251</t>
+          <t>5834399</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,12%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>354118</t>
+          <t>353740</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1215593</t>
+          <t>1196449</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>407643</t>
+          <t>408919</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>545874</t>
+          <t>543627</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,17 +8444,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1080041</t>
+          <t>1080042</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>836306</t>
+          <t>833123</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1875775</t>
+          <t>1837420</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>118263</t>
+          <t>118895</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>177665</t>
+          <t>176058</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>226816</t>
+          <t>226811</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>309571</t>
+          <t>308396</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8547,7 +8547,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>376454</t>
+          <t>376980</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>476017</t>
+          <t>473083</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7104362</t>
+          <t>7104363</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7104362</t>
+          <t>7104363</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7104362</t>
+          <t>7104363</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">

--- a/data/trans_orig/P0802-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P0802-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>693063</t>
+          <t>694721</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>753188</t>
+          <t>751651</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>680561</t>
+          <t>681004</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>755191</t>
+          <t>752904</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1394318</t>
+          <t>1390622</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1489494</t>
+          <t>1481169</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,11%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>196135</t>
+          <t>196242</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>246328</t>
+          <t>247664</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>400256</t>
+          <t>399716</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>467942</t>
+          <t>469013</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>608060</t>
+          <t>617157</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>694805</t>
+          <t>698690</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,77%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>70629</t>
+          <t>70358</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>105507</t>
+          <t>105359</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>141665</t>
+          <t>142495</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>190105</t>
+          <t>190869</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>224528</t>
+          <t>222734</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>282932</t>
+          <t>283095</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1559416</t>
+          <t>1557143</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1599721</t>
+          <t>1597879</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1427202</t>
+          <t>1425608</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1472327</t>
+          <t>1470231</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3000792</t>
+          <t>3000993</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3059082</t>
+          <t>3058781</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,22%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72392</t>
+          <t>74022</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>110250</t>
+          <t>111121</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>80704</t>
+          <t>82377</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>119693</t>
+          <t>120918</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>163859</t>
+          <t>165447</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>217251</t>
+          <t>219533</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15215</t>
+          <t>14924</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33411</t>
+          <t>33212</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27042</t>
+          <t>26648</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50686</t>
+          <t>50712</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46454</t>
+          <t>46423</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77159</t>
+          <t>76669</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>503162</t>
+          <t>502452</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>528323</t>
+          <t>528399</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>410798</t>
+          <t>411610</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>439716</t>
+          <t>439298</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>923111</t>
+          <t>923397</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>961000</t>
+          <t>961306</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14494</t>
+          <t>14857</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35998</t>
+          <t>35208</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27766</t>
+          <t>28132</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53715</t>
+          <t>53735</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48520</t>
+          <t>48925</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80905</t>
+          <t>81768</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21345</t>
+          <t>19569</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5597</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18747</t>
+          <t>18132</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12925</t>
+          <t>13080</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32940</t>
+          <t>32876</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2780770</t>
+          <t>2781322</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2860304</t>
+          <t>2860798</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2542685</t>
+          <t>2541509</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2641918</t>
+          <t>2635796</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5353005</t>
+          <t>5346904</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5475675</t>
+          <t>5479648</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,33%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>301996</t>
+          <t>302022</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>371394</t>
+          <t>371413</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>532418</t>
+          <t>532922</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>623494</t>
+          <t>622391</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>852849</t>
+          <t>846942</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>960674</t>
+          <t>962980</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>101039</t>
+          <t>100447</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>143626</t>
+          <t>143189</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>184782</t>
+          <t>185594</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>243533</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>301104</t>
+          <t>297939</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>371522</t>
+          <t>369738</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>618146</t>
+          <t>620403</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>680832</t>
+          <t>680303</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>643770</t>
+          <t>640382</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>721779</t>
+          <t>718070</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1282634</t>
+          <t>1285645</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1379705</t>
+          <t>1386398</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,98%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>174298</t>
+          <t>174584</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>228237</t>
+          <t>225717</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>347008</t>
+          <t>350260</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>414576</t>
+          <t>418721</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>541639</t>
+          <t>538676</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>628770</t>
+          <t>623119</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>105011</t>
+          <t>104258</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>150185</t>
+          <t>149226</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>242411</t>
+          <t>245383</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>305417</t>
+          <t>305505</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>360253</t>
+          <t>359811</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>438533</t>
+          <t>433626</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1758164</t>
+          <t>1761803</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1811499</t>
+          <t>1812841</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1505376</t>
+          <t>1506562</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1568898</t>
+          <t>1565552</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3282329</t>
+          <t>3279974</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3362606</t>
+          <t>3358716</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,34%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>115008</t>
+          <t>112806</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>159754</t>
+          <t>157700</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>133698</t>
+          <t>133737</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>184169</t>
+          <t>181531</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>261240</t>
+          <t>262050</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>329122</t>
+          <t>330369</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25590</t>
+          <t>26325</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53439</t>
+          <t>52903</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,82 +3485,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>63597</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>49187</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>83182</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>101639</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>82500</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>126356</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>2,73%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>63597</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>46719</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>82836</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>4,71%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>101639</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>82026</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>124520</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>431005</t>
+          <t>430993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>456401</t>
+          <t>456577</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>406728</t>
+          <t>406276</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>430954</t>
+          <t>431306</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>847270</t>
+          <t>844189</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>881082</t>
+          <t>881027</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16213</t>
+          <t>14935</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38190</t>
+          <t>37368</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19707</t>
+          <t>18972</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42254</t>
+          <t>40459</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40860</t>
+          <t>39651</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70955</t>
+          <t>73811</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21871</t>
+          <t>21870</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18408</t>
+          <t>16749</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12479</t>
+          <t>12151</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32269</t>
+          <t>32600</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2841998</t>
+          <t>2835188</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2928321</t>
+          <t>2927078</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2590538</t>
+          <t>2589037</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2694212</t>
+          <t>2687708</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5455302</t>
+          <t>5454320</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5592041</t>
+          <t>5592708</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,25%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>325218</t>
+          <t>322504</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>396518</t>
+          <t>396701</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>527652</t>
+          <t>522676</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>613975</t>
+          <t>610929</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>866673</t>
+          <t>874749</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>992009</t>
+          <t>990332</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>146872</t>
+          <t>148804</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>202200</t>
+          <t>203568</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>308368</t>
+          <t>310906</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>383106</t>
+          <t>382029</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>473482</t>
+          <t>474783</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>565816</t>
+          <t>566151</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>470715</t>
+          <t>476898</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>523161</t>
+          <t>524168</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>473128</t>
+          <t>474673</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>541951</t>
+          <t>542005</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>966462</t>
+          <t>971247</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1053098</t>
+          <t>1056565</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,41%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>138579</t>
+          <t>138284</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>181512</t>
+          <t>180668</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>249149</t>
+          <t>249799</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>309276</t>
+          <t>307788</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>396113</t>
+          <t>398629</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>473672</t>
+          <t>475326</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,18%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76992</t>
+          <t>78779</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>112518</t>
+          <t>115202</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>181177</t>
+          <t>182627</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>238740</t>
+          <t>236384</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>275081</t>
+          <t>271909</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>341794</t>
+          <t>337930</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1852212</t>
+          <t>1853003</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1908508</t>
+          <t>1906389</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1681880</t>
+          <t>1680914</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1746242</t>
+          <t>1748193</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3551320</t>
+          <t>3549329</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3633735</t>
+          <t>3635604</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,44%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>124134</t>
+          <t>124736</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>175199</t>
+          <t>172787</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>159853</t>
+          <t>156334</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>210982</t>
+          <t>214498</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>300240</t>
+          <t>300019</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>371765</t>
+          <t>369097</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35164</t>
+          <t>33674</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63786</t>
+          <t>63173</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70825</t>
+          <t>71932</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>110542</t>
+          <t>109046</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>115065</t>
+          <t>112706</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>162779</t>
+          <t>161930</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>487943</t>
+          <t>488062</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>514832</t>
+          <t>516674</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>487617</t>
+          <t>487446</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>516084</t>
+          <t>516320</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>986828</t>
+          <t>985867</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1026049</t>
+          <t>1025332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,55%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21722</t>
+          <t>21571</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46609</t>
+          <t>46833</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19003</t>
+          <t>19192</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42284</t>
+          <t>44157</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45566</t>
+          <t>47296</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80234</t>
+          <t>80595</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5660</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19730</t>
+          <t>19384</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9267</t>
+          <t>8883</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27425</t>
+          <t>28221</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17929</t>
+          <t>16602</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41396</t>
+          <t>40265</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2844492</t>
+          <t>2843671</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2925802</t>
+          <t>2925972</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2669453</t>
+          <t>2672116</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2778810</t>
+          <t>2780234</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5547860</t>
+          <t>5545686</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5674869</t>
+          <t>5679542</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,2%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>306258</t>
+          <t>303950</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>374425</t>
+          <t>374563</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>449960</t>
+          <t>449240</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>534134</t>
+          <t>538513</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>775378</t>
+          <t>775752</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>884801</t>
+          <t>887850</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>130412</t>
+          <t>130758</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>179651</t>
+          <t>178841</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>281476</t>
+          <t>282427</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>358064</t>
+          <t>355215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>429121</t>
+          <t>428370</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>517255</t>
+          <t>512354</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -6893,32 +6893,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>331633</t>
+          <t>382057</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>310477</t>
+          <t>359590</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>350432</t>
+          <t>402129</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6928,32 +6928,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>342734</t>
+          <t>381318</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>321408</t>
+          <t>359044</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>364117</t>
+          <t>403149</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>674367</t>
+          <t>763375</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>645530</t>
+          <t>734254</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>703215</t>
+          <t>797223</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>56,94%</t>
         </is>
       </c>
     </row>
@@ -7006,32 +7006,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>104512</t>
+          <t>112141</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91365</t>
+          <t>94401</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>122896</t>
+          <t>129949</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>226983</t>
+          <t>238778</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>207304</t>
+          <t>219243</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>245748</t>
+          <t>259336</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>331495</t>
+          <t>350919</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>305821</t>
+          <t>324180</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>358435</t>
+          <t>378055</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,0%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>78793</t>
+          <t>84331</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65353</t>
+          <t>70148</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>93841</t>
+          <t>101107</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>185218</t>
+          <t>201365</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>167629</t>
+          <t>183577</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>202408</t>
+          <t>221740</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>264011</t>
+          <t>285696</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>241712</t>
+          <t>263668</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>287748</t>
+          <t>311847</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>754935</t>
+          <t>821462</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>754935</t>
+          <t>821462</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>754935</t>
+          <t>821462</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1269873</t>
+          <t>1399991</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1269873</t>
+          <t>1399991</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1269873</t>
+          <t>1399991</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7349,32 +7349,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1782718</t>
+          <t>1946889</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1203371</t>
+          <t>1913668</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2007315</t>
+          <t>1977333</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7384,32 +7384,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1938434</t>
+          <t>1836476</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1894977</t>
+          <t>1809082</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2019373</t>
+          <t>1863650</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3721152</t>
+          <t>3783366</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3007035</t>
+          <t>3741100</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3952632</t>
+          <t>3821109</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>86,8%</t>
         </is>
       </c>
     </row>
@@ -7462,32 +7462,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>446896</t>
+          <t>219608</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>217030</t>
+          <t>194865</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1056913</t>
+          <t>250082</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7497,32 +7497,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>225023</t>
+          <t>252519</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>164655</t>
+          <t>229711</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>262315</t>
+          <t>277216</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>671919</t>
+          <t>472128</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>437735</t>
+          <t>436647</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1407661</t>
+          <t>511606</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>60713</t>
+          <t>64069</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41169</t>
+          <t>49370</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79803</t>
+          <t>79945</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>74365</t>
+          <t>82397</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54139</t>
+          <t>68605</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90330</t>
+          <t>97845</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>135078</t>
+          <t>146466</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>106419</t>
+          <t>127342</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159869</t>
+          <t>168749</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -7688,17 +7688,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7723,17 +7723,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7805,32 +7805,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>602131</t>
+          <t>661793</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>589637</t>
+          <t>647290</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>611658</t>
+          <t>673117</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7840,32 +7840,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>600215</t>
+          <t>662855</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>587951</t>
+          <t>648362</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>611023</t>
+          <t>674006</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1202346</t>
+          <t>1324648</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1186618</t>
+          <t>1305039</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1218713</t>
+          <t>1341262</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -7918,17 +7918,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>32213</t>
+          <t>35461</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23133</t>
+          <t>25869</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43480</t>
+          <t>48325</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7953,32 +7953,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>44415</t>
+          <t>51258</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35200</t>
+          <t>40851</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54298</t>
+          <t>61805</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>76627</t>
+          <t>86719</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62272</t>
+          <t>72491</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90429</t>
+          <t>103155</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -8031,32 +8031,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11532</t>
+          <t>13459</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6993</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19437</t>
+          <t>21707</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8066,32 +8066,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>15833</t>
+          <t>20764</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10471</t>
+          <t>14067</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>29806</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>27366</t>
+          <t>34223</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19913</t>
+          <t>24975</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37929</t>
+          <t>45354</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -8144,17 +8144,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>645876</t>
+          <t>710713</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>645876</t>
+          <t>710713</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>645876</t>
+          <t>710713</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1306339</t>
+          <t>1445590</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1306339</t>
+          <t>1445590</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1306339</t>
+          <t>1445590</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2716483</t>
+          <t>2990739</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2144647</t>
+          <t>2947737</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2937065</t>
+          <t>3032536</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2881383</t>
+          <t>2880650</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2813893</t>
+          <t>2835888</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3019975</t>
+          <t>2920717</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5597866</t>
+          <t>5871389</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4889661</t>
+          <t>5809830</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5834399</t>
+          <t>5929043</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>81,81%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>583621</t>
+          <t>367211</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>353740</t>
+          <t>334705</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1196449</t>
+          <t>409285</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>496421</t>
+          <t>542555</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>408919</t>
+          <t>507020</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>543627</t>
+          <t>577963</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1080042</t>
+          <t>909766</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>833123</t>
+          <t>861213</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1837420</t>
+          <t>959795</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>151039</t>
+          <t>161859</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>118895</t>
+          <t>139475</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>176058</t>
+          <t>189629</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>275417</t>
+          <t>304526</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>226811</t>
+          <t>278653</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>308396</t>
+          <t>331490</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>426456</t>
+          <t>466385</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>376980</t>
+          <t>432687</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>473083</t>
+          <t>501258</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3451142</t>
+          <t>3519809</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3451142</t>
+          <t>3519809</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3451142</t>
+          <t>3519809</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3653221</t>
+          <t>3727731</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3653221</t>
+          <t>3727731</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3653221</t>
+          <t>3727731</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7104363</t>
+          <t>7247540</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7104363</t>
+          <t>7247540</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7104363</t>
+          <t>7247540</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
